--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934397</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934397</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2887,6 +2887,1425 @@
       <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136934398</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137381620</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516149</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6721065</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381620</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137381622</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516131</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6721050</v>
+      </c>
+      <c r="S22" t="n">
+        <v>14</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>50 plantor</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381622</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137381623</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>516123</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6721073</v>
+      </c>
+      <c r="S23" t="n">
+        <v>16</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381623</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137381626</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>516079</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6721087</v>
+      </c>
+      <c r="S24" t="n">
+        <v>26</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381626</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137381627</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>516096</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6721124</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10 plantor</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381627</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137381628</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>516120</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6721113</v>
+      </c>
+      <c r="S26" t="n">
+        <v>14</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>100 plantor</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381628</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137381629</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>516126</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6721144</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381629</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137381630</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>516134</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6721137</v>
+      </c>
+      <c r="S28" t="n">
+        <v>7</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381630</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137381632</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>516180</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6721159</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381632</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137381634</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>516060</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6721175</v>
+      </c>
+      <c r="S30" t="n">
+        <v>11</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381634</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137381635</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99412</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>516050</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6721187</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>20 plantor</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381635</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137381625</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gravertjärnen Valsan 2, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>516116</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6721082</v>
+      </c>
+      <c r="S32" t="n">
+        <v>11</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1 m2</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137381625</t>
         </is>
       </c>
     </row>
@@ -2911,6 +4330,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934397</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>137381620</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>137381622</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137381623</v>
       </c>
       <c r="B23" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137381626</v>
       </c>
       <c r="B24" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137381627</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>137381628</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137381629</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137381630</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137381632</v>
       </c>
       <c r="B29" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137381634</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>137381635</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>137381625</v>
       </c>
       <c r="B32" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>137381620</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>137381622</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137381623</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137381626</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137381627</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>137381628</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137381629</v>
       </c>
       <c r="B27" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137381630</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137381632</v>
       </c>
       <c r="B29" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137381634</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>137381635</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>137381625</v>
       </c>
       <c r="B32" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>137381620</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>137381622</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137381623</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137381626</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137381627</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>137381628</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137381629</v>
       </c>
       <c r="B27" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137381630</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137381632</v>
       </c>
       <c r="B29" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137381634</v>
       </c>
       <c r="B30" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>137381635</v>
       </c>
       <c r="B31" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>137381625</v>
       </c>
       <c r="B32" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>137381620</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>137381622</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137381623</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137381626</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137381627</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>137381628</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137381629</v>
       </c>
       <c r="B27" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137381630</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137381632</v>
       </c>
       <c r="B29" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137381634</v>
       </c>
       <c r="B30" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>137381635</v>
       </c>
       <c r="B31" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>137381625</v>
       </c>
       <c r="B32" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 42880-2026 artfynd.xlsx
+++ b/artfynd/A 42880-2026 artfynd.xlsx
@@ -1614,7 +1614,7 @@
         <v>136934394</v>
       </c>
       <c r="B10" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>136934397</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>136934396</v>
       </c>
       <c r="B19" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         <v>136934398</v>
       </c>
       <c r="B20" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
         <v>137381620</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
         <v>137381622</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>137381623</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137381626</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137381627</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>137381628</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>137381629</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137381630</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137381632</v>
       </c>
       <c r="B29" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>137381634</v>
       </c>
       <c r="B30" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>137381635</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>137381625</v>
       </c>
       <c r="B32" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
